--- a/InputData/io-model/VoSTR/VAT or Sales Tax Rate.xlsx
+++ b/InputData/io-model/VoSTR/VAT or Sales Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\olivia\Documents\EPS_Models by Region\RMI\RMI_all_states\OR\io-model\VoSTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan\Documents\state-eps-data-repository\OR\io-model\VoSTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A674513A-8D8A-4FBB-A405-ED307E0752BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{083BED7A-7EA8-471C-BE2E-FF60075FDCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13560" yWindow="6780" windowWidth="15240" windowHeight="10545" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Average Tax Rate" sheetId="5" r:id="rId5"/>
     <sheet name="VoSTR" sheetId="2" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1516,7 +1516,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1551,21 +1551,25 @@
       <b/>
       <sz val="14"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="13"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color indexed="9"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1584,11 +1588,13 @@
       <i/>
       <sz val="15"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -1762,9 +1768,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1802,9 +1808,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1837,26 +1843,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1889,26 +1878,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2083,7 +2055,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.85546875" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
@@ -2091,7 +2063,7 @@
     <col min="5" max="6" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -2099,7 +2071,7 @@
         <v>408</v>
       </c>
       <c r="C1" s="16">
-        <v>44827</v>
+        <v>45298</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>335</v>
@@ -2108,7 +2080,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="13" t="str">
         <f>INDEX(F:F,MATCH(B1,E:E,0))</f>
         <v>OR</v>
@@ -2121,7 +2093,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>329</v>
       </c>
@@ -2138,7 +2110,7 @@
       </c>
       <c r="G3" s="10"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="14" t="s">
         <v>331</v>
       </c>
@@ -2149,7 +2121,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="14">
         <v>2022</v>
       </c>
@@ -2160,7 +2132,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="14" t="s">
         <v>49</v>
       </c>
@@ -2171,7 +2143,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="14" t="s">
         <v>332</v>
       </c>
@@ -2182,7 +2154,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="E8" s="13" t="s">
         <v>348</v>
       </c>
@@ -2190,7 +2162,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
         <v>330</v>
       </c>
@@ -2204,7 +2176,7 @@
       </c>
       <c r="G9" s="10"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="14" t="s">
         <v>331</v>
       </c>
@@ -2215,7 +2187,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="14">
         <v>2022</v>
       </c>
@@ -2226,7 +2198,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="14" t="s">
         <v>228</v>
       </c>
@@ -2237,7 +2209,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="14" t="s">
         <v>333</v>
       </c>
@@ -2248,7 +2220,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="14"/>
       <c r="E14" s="13" t="s">
         <v>360</v>
@@ -2257,7 +2229,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>487</v>
       </c>
@@ -2268,7 +2240,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="14" t="s">
         <v>488</v>
       </c>
@@ -2279,7 +2251,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B17" s="14">
         <v>2022</v>
       </c>
@@ -2290,7 +2262,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="14" t="s">
         <v>486</v>
       </c>
@@ -2301,7 +2273,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="14" t="s">
         <v>489</v>
       </c>
@@ -2312,7 +2284,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E20" s="13" t="s">
         <v>372</v>
       </c>
@@ -2320,7 +2292,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E21" s="13" t="s">
         <v>374</v>
       </c>
@@ -2328,7 +2300,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E22" s="13" t="s">
         <v>376</v>
       </c>
@@ -2336,7 +2308,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E23" s="13" t="s">
         <v>378</v>
       </c>
@@ -2344,7 +2316,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E24" s="13" t="s">
         <v>380</v>
       </c>
@@ -2352,7 +2324,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E25" s="13" t="s">
         <v>382</v>
       </c>
@@ -2360,7 +2332,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>0</v>
       </c>
@@ -2371,7 +2343,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -2382,7 +2354,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E28" s="13" t="s">
         <v>388</v>
       </c>
@@ -2390,7 +2362,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>47</v>
       </c>
@@ -2401,7 +2373,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -2412,7 +2384,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E31" s="13" t="s">
         <v>394</v>
       </c>
@@ -2420,7 +2392,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>326</v>
       </c>
@@ -2431,7 +2403,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>327</v>
       </c>
@@ -2442,7 +2414,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>328</v>
       </c>
@@ -2453,7 +2425,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E35" s="13" t="s">
         <v>402</v>
       </c>
@@ -2461,7 +2433,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E36" s="13" t="s">
         <v>404</v>
       </c>
@@ -2469,7 +2441,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E37" s="13" t="s">
         <v>406</v>
       </c>
@@ -2477,7 +2449,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E38" s="13" t="s">
         <v>408</v>
       </c>
@@ -2485,7 +2457,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E39" s="13" t="s">
         <v>410</v>
       </c>
@@ -2493,7 +2465,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E40" s="13" t="s">
         <v>412</v>
       </c>
@@ -2501,7 +2473,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E41" s="13" t="s">
         <v>414</v>
       </c>
@@ -2509,7 +2481,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E42" s="13" t="s">
         <v>416</v>
       </c>
@@ -2517,7 +2489,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E43" s="13" t="s">
         <v>418</v>
       </c>
@@ -2525,7 +2497,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E44" s="13" t="s">
         <v>420</v>
       </c>
@@ -2533,7 +2505,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E45" s="13" t="s">
         <v>422</v>
       </c>
@@ -2541,7 +2513,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E46" s="13" t="s">
         <v>424</v>
       </c>
@@ -2549,7 +2521,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E47" s="13" t="s">
         <v>426</v>
       </c>
@@ -2557,7 +2529,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E48" s="13" t="s">
         <v>428</v>
       </c>
@@ -2565,7 +2537,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="49" spans="5:6">
+    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E49" s="13" t="s">
         <v>334</v>
       </c>
@@ -2573,7 +2545,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="50" spans="5:6">
+    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E50" s="13" t="s">
         <v>431</v>
       </c>
@@ -2581,7 +2553,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="51" spans="5:6">
+    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
       <c r="E51" s="13" t="s">
         <v>433</v>
       </c>
@@ -2598,17 +2570,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4808E40E-62AC-4DD4-A7AE-69521F9CF108}">
   <dimension ref="A1:H53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75">
+    <row r="1" spans="1:8" ht="27.75" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="19" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>335</v>
       </c>
@@ -2631,7 +2603,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>337</v>
       </c>
@@ -2657,7 +2629,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>339</v>
       </c>
@@ -2683,7 +2655,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>341</v>
       </c>
@@ -2709,7 +2681,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
         <v>343</v>
       </c>
@@ -2735,7 +2707,7 @@
         <v>6.1249999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>345</v>
       </c>
@@ -2761,7 +2733,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
         <v>347</v>
       </c>
@@ -2787,7 +2759,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>349</v>
       </c>
@@ -2813,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
         <v>351</v>
       </c>
@@ -2839,7 +2811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>447</v>
       </c>
@@ -2862,7 +2834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
         <v>353</v>
       </c>
@@ -2888,7 +2860,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>355</v>
       </c>
@@ -2914,7 +2886,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
         <v>357</v>
       </c>
@@ -2940,7 +2912,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>359</v>
       </c>
@@ -2966,7 +2938,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>361</v>
       </c>
@@ -2992,7 +2964,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>363</v>
       </c>
@@ -3018,7 +2990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
         <v>365</v>
       </c>
@@ -3044,7 +3016,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>367</v>
       </c>
@@ -3070,7 +3042,7 @@
         <v>4.2500000000000003E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>369</v>
       </c>
@@ -3096,7 +3068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>371</v>
       </c>
@@ -3122,7 +3094,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
         <v>373</v>
       </c>
@@ -3148,7 +3120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>375</v>
       </c>
@@ -3174,7 +3146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
         <v>377</v>
       </c>
@@ -3200,7 +3172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>379</v>
       </c>
@@ -3226,7 +3198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
         <v>381</v>
       </c>
@@ -3252,7 +3224,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>383</v>
       </c>
@@ -3278,7 +3250,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
         <v>385</v>
       </c>
@@ -3304,7 +3276,7 @@
         <v>5.7630000000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>387</v>
       </c>
@@ -3330,7 +3302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
         <v>389</v>
       </c>
@@ -3356,7 +3328,7 @@
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>391</v>
       </c>
@@ -3382,7 +3354,7 @@
         <v>1.5299999999999999E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
         <v>393</v>
       </c>
@@ -3408,7 +3380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>395</v>
       </c>
@@ -3434,7 +3406,7 @@
         <v>3.313E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
         <v>397</v>
       </c>
@@ -3460,7 +3432,7 @@
         <v>4.3130000000000002E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>399</v>
       </c>
@@ -3486,7 +3458,7 @@
         <v>4.8750000000000002E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
         <v>401</v>
       </c>
@@ -3512,7 +3484,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>403</v>
       </c>
@@ -3538,7 +3510,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
         <v>405</v>
       </c>
@@ -3564,7 +3536,7 @@
         <v>2.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>407</v>
       </c>
@@ -3590,7 +3562,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>409</v>
       </c>
@@ -3616,7 +3588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>411</v>
       </c>
@@ -3642,7 +3614,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>413</v>
       </c>
@@ -3668,7 +3640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>415</v>
       </c>
@@ -3694,7 +3666,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="13" t="s">
         <v>417</v>
       </c>
@@ -3720,7 +3692,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>419</v>
       </c>
@@ -3746,7 +3718,7 @@
         <v>2.75E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="13" t="s">
         <v>421</v>
       </c>
@@ -3772,7 +3744,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>423</v>
       </c>
@@ -3798,7 +3770,7 @@
         <v>2.9499999999999998E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="13" t="s">
         <v>425</v>
       </c>
@@ -3824,7 +3796,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>427</v>
       </c>
@@ -3850,7 +3822,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
         <v>429</v>
       </c>
@@ -3876,7 +3848,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>430</v>
       </c>
@@ -3902,7 +3874,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="13" t="s">
         <v>432</v>
       </c>
@@ -3928,7 +3900,7 @@
         <v>1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>434</v>
       </c>
@@ -3962,7 +3934,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6BFE65BF-AB38-4432-8FBE-6BE791426801}">
   <dimension ref="A1:CH81"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="36.28515625" customWidth="1"/>
     <col min="3" max="84" width="0" hidden="1" customWidth="1"/>
@@ -3970,7 +3942,7 @@
     <col min="86" max="86" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:86" ht="18">
+    <row r="1" spans="1:86" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>49</v>
       </c>
@@ -4059,7 +4031,7 @@
       <c r="CF1" s="23"/>
       <c r="CG1" s="23"/>
     </row>
-    <row r="2" spans="1:86" ht="16.5">
+    <row r="2" spans="1:86" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>50</v>
       </c>
@@ -4148,7 +4120,7 @@
       <c r="CF2" s="23"/>
       <c r="CG2" s="23"/>
     </row>
-    <row r="3" spans="1:86">
+    <row r="3" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>51</v>
       </c>
@@ -4237,7 +4209,7 @@
       <c r="CF3" s="23"/>
       <c r="CG3" s="23"/>
     </row>
-    <row r="4" spans="1:86">
+    <row r="4" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>52</v>
       </c>
@@ -4326,7 +4298,7 @@
       <c r="CF4" s="23"/>
       <c r="CG4" s="23"/>
     </row>
-    <row r="6" spans="1:86">
+    <row r="6" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>52</v>
       </c>
@@ -4583,7 +4555,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="7" spans="1:86">
+    <row r="7" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="4" t="s">
         <v>137</v>
@@ -4841,7 +4813,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="8" spans="1:86">
+    <row r="8" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -5101,7 +5073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:86">
+    <row r="9" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -5361,7 +5333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:86">
+    <row r="10" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -5621,7 +5593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:86">
+    <row r="11" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -5881,7 +5853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:86">
+    <row r="12" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -6141,7 +6113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:86">
+    <row r="13" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -6401,7 +6373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:86">
+    <row r="14" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>60</v>
       </c>
@@ -6661,7 +6633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:86">
+    <row r="15" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>61</v>
       </c>
@@ -6921,7 +6893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:86">
+    <row r="16" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>62</v>
       </c>
@@ -7181,7 +7153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:86">
+    <row r="17" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -7441,7 +7413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:86">
+    <row r="18" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -7701,7 +7673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:86">
+    <row r="19" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -7961,7 +7933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:86">
+    <row r="20" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -8221,7 +8193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:86">
+    <row r="21" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -8481,7 +8453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:86">
+    <row r="22" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>68</v>
       </c>
@@ -8741,7 +8713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:86">
+    <row r="23" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>69</v>
       </c>
@@ -9001,7 +8973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:86">
+    <row r="24" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>70</v>
       </c>
@@ -9261,7 +9233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:86">
+    <row r="25" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -9521,7 +9493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:86">
+    <row r="26" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -9781,7 +9753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:86">
+    <row r="27" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>73</v>
       </c>
@@ -10041,7 +10013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:86">
+    <row r="28" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -10301,7 +10273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:86">
+    <row r="29" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>75</v>
       </c>
@@ -10561,7 +10533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:86">
+    <row r="30" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>76</v>
       </c>
@@ -10821,7 +10793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:86">
+    <row r="31" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -11081,7 +11053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:86">
+    <row r="32" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>78</v>
       </c>
@@ -11341,7 +11313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:86">
+    <row r="33" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -11601,7 +11573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:86">
+    <row r="34" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>80</v>
       </c>
@@ -11861,7 +11833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:86">
+    <row r="35" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -12121,7 +12093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:86">
+    <row r="36" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -12381,7 +12353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:86">
+    <row r="37" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -12641,7 +12613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:86">
+    <row r="38" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>84</v>
       </c>
@@ -12901,7 +12873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:86">
+    <row r="39" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>85</v>
       </c>
@@ -13161,7 +13133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:86">
+    <row r="40" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>86</v>
       </c>
@@ -13421,7 +13393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:86">
+    <row r="41" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>87</v>
       </c>
@@ -13681,7 +13653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:86">
+    <row r="42" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>88</v>
       </c>
@@ -13941,7 +13913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:86">
+    <row r="43" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>89</v>
       </c>
@@ -14201,7 +14173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:86">
+    <row r="44" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>90</v>
       </c>
@@ -14461,7 +14433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:86">
+    <row r="45" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>91</v>
       </c>
@@ -14721,7 +14693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:86">
+    <row r="46" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>92</v>
       </c>
@@ -14981,7 +14953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:86">
+    <row r="47" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>93</v>
       </c>
@@ -15241,7 +15213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:86">
+    <row r="48" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -15501,7 +15473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:86">
+    <row r="49" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>95</v>
       </c>
@@ -15761,7 +15733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:86">
+    <row r="50" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>96</v>
       </c>
@@ -16021,7 +15993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:86">
+    <row r="51" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>97</v>
       </c>
@@ -16281,7 +16253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:86">
+    <row r="52" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>98</v>
       </c>
@@ -16541,7 +16513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:86">
+    <row r="53" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>99</v>
       </c>
@@ -16801,7 +16773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:86">
+    <row r="54" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>100</v>
       </c>
@@ -17061,7 +17033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:86">
+    <row r="55" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>101</v>
       </c>
@@ -17321,7 +17293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:86">
+    <row r="56" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>102</v>
       </c>
@@ -17581,7 +17553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:86">
+    <row r="57" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>103</v>
       </c>
@@ -17841,7 +17813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:86">
+    <row r="58" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>104</v>
       </c>
@@ -18101,7 +18073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:86">
+    <row r="59" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>105</v>
       </c>
@@ -18361,7 +18333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:86">
+    <row r="60" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>106</v>
       </c>
@@ -18621,7 +18593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:86">
+    <row r="61" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>107</v>
       </c>
@@ -18881,7 +18853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:86">
+    <row r="62" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>108</v>
       </c>
@@ -19141,7 +19113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:86">
+    <row r="63" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>109</v>
       </c>
@@ -19401,7 +19373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:86">
+    <row r="64" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>110</v>
       </c>
@@ -19661,7 +19633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:86">
+    <row r="65" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>111</v>
       </c>
@@ -19921,7 +19893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:86">
+    <row r="66" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>112</v>
       </c>
@@ -20181,7 +20153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:86">
+    <row r="67" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>113</v>
       </c>
@@ -20441,7 +20413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:86">
+    <row r="68" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>114</v>
       </c>
@@ -20701,7 +20673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:86">
+    <row r="69" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>115</v>
       </c>
@@ -20961,7 +20933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:86">
+    <row r="70" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>116</v>
       </c>
@@ -21221,7 +21193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:86">
+    <row r="71" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>117</v>
       </c>
@@ -21481,7 +21453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:86">
+    <row r="72" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>118</v>
       </c>
@@ -21741,7 +21713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:86">
+    <row r="73" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>119</v>
       </c>
@@ -22001,7 +21973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:86">
+    <row r="74" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>120</v>
       </c>
@@ -22261,7 +22233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:86">
+    <row r="75" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>121</v>
       </c>
@@ -22521,7 +22493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:86">
+    <row r="76" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>122</v>
       </c>
@@ -22781,7 +22753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:86">
+    <row r="77" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>123</v>
       </c>
@@ -23041,7 +23013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:86">
+    <row r="78" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>124</v>
       </c>
@@ -23301,7 +23273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:86">
+    <row r="79" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>222</v>
       </c>
@@ -23561,7 +23533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:86">
+    <row r="80" spans="1:86" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>224</v>
       </c>
@@ -23821,7 +23793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:85">
+    <row r="81" spans="1:85" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>226</v>
       </c>
@@ -24094,12 +24066,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27130C2E-0479-46E8-A0A0-BE00F4868B20}">
   <dimension ref="A1:K54"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="32.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>228</v>
       </c>
@@ -24114,7 +24086,7 @@
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
     </row>
-    <row r="2" spans="1:11" ht="16.5">
+    <row r="2" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>229</v>
       </c>
@@ -24129,7 +24101,7 @@
       <c r="J2" s="23"/>
       <c r="K2" s="23"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>51</v>
       </c>
@@ -24144,7 +24116,7 @@
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
         <v>230</v>
       </c>
@@ -24159,7 +24131,7 @@
       <c r="J4" s="23"/>
       <c r="K4" s="23"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>231</v>
       </c>
@@ -24182,7 +24154,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="25"/>
       <c r="C7" s="4" t="s">
@@ -24213,7 +24185,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>239</v>
       </c>
@@ -24248,7 +24220,7 @@
         <v>3557.4</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>241</v>
       </c>
@@ -24283,7 +24255,7 @@
         <v>2368.1999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>243</v>
       </c>
@@ -24318,7 +24290,7 @@
         <v>671.7</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>245</v>
       </c>
@@ -24353,7 +24325,7 @@
         <v>629.9</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>247</v>
       </c>
@@ -24388,7 +24360,7 @@
         <v>41.7</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>249</v>
       </c>
@@ -24423,7 +24395,7 @@
         <v>1541.1</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>251</v>
       </c>
@@ -24458,7 +24430,7 @@
         <v>533.70000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>253</v>
       </c>
@@ -24493,7 +24465,7 @@
         <v>226.5</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>255</v>
       </c>
@@ -24528,7 +24500,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>257</v>
       </c>
@@ -24563,7 +24535,7 @@
         <v>129.9</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>258</v>
       </c>
@@ -24598,7 +24570,7 @@
         <v>155.4</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>260</v>
       </c>
@@ -24633,7 +24605,7 @@
         <v>22.9</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>262</v>
       </c>
@@ -24668,7 +24640,7 @@
         <v>100.5</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>264</v>
       </c>
@@ -24703,7 +24675,7 @@
         <v>79.7</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>266</v>
       </c>
@@ -24738,7 +24710,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>268</v>
       </c>
@@ -24773,7 +24745,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>270</v>
       </c>
@@ -24808,7 +24780,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>272</v>
       </c>
@@ -24843,7 +24815,7 @@
         <v>916.3</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>274</v>
       </c>
@@ -24878,7 +24850,7 @@
         <v>61.7</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>276</v>
       </c>
@@ -24913,7 +24885,7 @@
         <v>96.9</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>278</v>
       </c>
@@ -24948,7 +24920,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -24983,7 +24955,7 @@
         <v>-9.3000000000000007</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>60</v>
       </c>
@@ -25018,7 +24990,7 @@
         <v>3413.7</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>282</v>
       </c>
@@ -25053,7 +25025,7 @@
         <v>2180.3000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>284</v>
       </c>
@@ -25088,7 +25060,7 @@
         <v>948.5</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>286</v>
       </c>
@@ -25123,7 +25095,7 @@
         <v>948.5</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>288</v>
       </c>
@@ -25158,7 +25130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>290</v>
       </c>
@@ -25193,7 +25165,7 @@
         <v>284.2</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>292</v>
       </c>
@@ -25228,7 +25200,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>294</v>
       </c>
@@ -25263,7 +25235,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>296</v>
       </c>
@@ -25298,7 +25270,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>297</v>
       </c>
@@ -25333,7 +25305,7 @@
         <v>143.6</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>299</v>
       </c>
@@ -25368,7 +25340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>301</v>
       </c>
@@ -25403,7 +25375,7 @@
         <v>137.6</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>52</v>
       </c>
@@ -25438,7 +25410,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>303</v>
       </c>
@@ -25473,7 +25445,7 @@
         <v>3641</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>305</v>
       </c>
@@ -25508,7 +25480,7 @@
         <v>3557.4</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>306</v>
       </c>
@@ -25543,7 +25515,7 @@
         <v>83.7</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>308</v>
       </c>
@@ -25578,7 +25550,7 @@
         <v>3532.3</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>310</v>
       </c>
@@ -25613,7 +25585,7 @@
         <v>3413.7</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>311</v>
       </c>
@@ -25648,7 +25620,7 @@
         <v>450.3</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>313</v>
       </c>
@@ -25683,7 +25655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>80</v>
       </c>
@@ -25718,7 +25690,7 @@
         <v>19.100000000000001</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>316</v>
       </c>
@@ -25753,7 +25725,7 @@
         <v>350.8</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>318</v>
       </c>
@@ -25788,7 +25760,7 @@
         <v>108.8</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.75">
+    <row r="53" spans="1:11" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A53" s="26" t="s">
         <v>320</v>
       </c>
@@ -25803,7 +25775,7 @@
       <c r="J53" s="23"/>
       <c r="K53" s="23"/>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="27" t="s">
         <v>321</v>
       </c>
@@ -25838,13 +25810,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D25AABD1-0D09-4A7E-A29B-4F41AA94F3B1}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.85546875" customWidth="1"/>
     <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>323</v>
       </c>
@@ -25853,7 +25825,7 @@
         <v>1795500000000</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>324</v>
       </c>
@@ -25862,7 +25834,7 @@
         <v>34904443000000</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>325</v>
       </c>
@@ -25882,13 +25854,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AQ2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" customWidth="1"/>
     <col min="2" max="2" width="26.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="30">
+    <row r="1" spans="1:43" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>45</v>
       </c>
@@ -26019,7 +25991,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:43">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>

--- a/InputData/io-model/VoSTR/VAT or Sales Tax Rate.xlsx
+++ b/InputData/io-model/VoSTR/VAT or Sales Tax Rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nathan\Documents\state-eps-data-repository\OR\io-model\VoSTR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\OR\io-model\VoSTR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{083BED7A-7EA8-471C-BE2E-FF60075FDCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{51D5B0DD-9ED3-4CB0-9972-E359034E07D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12510" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2071,7 +2071,7 @@
         <v>408</v>
       </c>
       <c r="C1" s="16">
-        <v>45298</v>
+        <v>46185</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>335</v>
